--- a/output/第10期計画素案_修正指示書_令和8年7月.xlsx
+++ b/output/第10期計画素案_修正指示書_令和8年7月.xlsx
@@ -2600,7 +2600,7 @@
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>見える化D49（令和5年・地域別）／見える化D42（介護サービス利用率）</t>
+          <t>見える化D49（令和5年・地域別）／見える化D42（介護サービス利用率）／D49の指標の解説（令和8年10月19日受領。受給率の分母は第1号被保険者数であることが確定した。4指標のうち性・年齢調整後であるのは第1号被保険者1人あたり給付月額と要介護認定率の2指標のみであり、地域差指数を乗法的に分解できないことも分かった）</t>
         </is>
       </c>
       <c r="J35" s="7" t="inlineStr">
